--- a/138_Cuenca_Chira/_raw_reportes_xlsx/IDConfig_64936_completo.xlsx
+++ b/138_Cuenca_Chira/_raw_reportes_xlsx/IDConfig_64936_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Re798a339a7e44ac3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R32443a6546b94b54"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.5564</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.5981</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     16.9036</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.1063</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.0380</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.2649</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     16.3309</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.4032</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4313</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/138_Cuenca_Chira/_raw_reportes_xlsx/IDConfig_64936_completo.xlsx
+++ b/138_Cuenca_Chira/_raw_reportes_xlsx/IDConfig_64936_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R32443a6546b94b54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R4b86a3044ca044d7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.5102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.1062</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.8121</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3688</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     16.1044</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.1056</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.6382</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.2630</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.5050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6795</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.8318</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.6687</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.0457</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.2595</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.0839</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.6156</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     19.2990</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.3580</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.2071</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.7451</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.3278</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     35.6686</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.4112</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.4611</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.8821</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.5159</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.3271</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.6085</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.5218</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.8499</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.1706</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.2984</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.9401</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.1047</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5198</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     16.5410</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     16.3594</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.0053</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.4047</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.3697</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.4343</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.5343</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.0246</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.6280</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.5467</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.9146</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.8817</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6398</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
